--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,594억   ·   현금 27억(0.6%)      주말 2026-10-23  vs  주초 2026-10-19      매수 16종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,380억      주말 2026-10-23  vs  주초 2026-10-19      매수 16종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>426</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4259932439</v>
+        <v>4259932097</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-176</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1647782632</v>
+        <v>-1647782499</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>142</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3443869684</v>
+        <v>3443869407</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-156</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2004350682</v>
+        <v>-2004350521</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>84</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3576636503</v>
+        <v>3576636215</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-50</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1319700186</v>
+        <v>-1319700080</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>78</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4661280655</v>
+        <v>4661280281</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2174069106</v>
+        <v>-2174068931</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>874079763</v>
+        <v>874079693</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1296792182</v>
+        <v>-1296792078</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2659320374</v>
+        <v>2659320160</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-26</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-408379977</v>
+        <v>-408379945</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1387975995</v>
+        <v>1387975884</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1142910161</v>
+        <v>-1142910069</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1321094586</v>
+        <v>1321094480</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2788302392</v>
+        <v>-2788302168</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2627547969</v>
+        <v>2627547758</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1226275372</v>
+        <v>-1226275274</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>430371660</v>
+        <v>430371626</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-7</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-758553707</v>
+        <v>-758553646</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1307250184</v>
+        <v>1307250079</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-122508017</v>
+        <v>-122508007</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>413539258</v>
+        <v>586245635</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.46%</t>
+          <t>0.43%→0.52%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1175,7 +1175,7 @@
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1048290147</v>
+        <v>-1048290063</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2958120416</v>
+        <v>413539225</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.10%</t>
+          <t>1.43%→1.46%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-671304094</v>
+        <v>-671304040</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>586245682</v>
+        <v>2958120178</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.52%</t>
+          <t>1.45%→2.10%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1270,7 +1270,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2070684291</v>
+        <v>2070684125</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>841420918</v>
+        <v>841420851</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,216억   ·   현금 60억(1.9%)      주말 2026-10-23  vs  주초 2026-10-19      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,140억      주말 2026-10-23  vs  주초 2026-10-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1343,7 +1343,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,348억   ·   현금 37억(1.7%)      주말 2026-10-23  vs  주초 2026-10-19      매수 14종목  /  매도 23종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,218억      주말 2026-10-23  vs  주초 2026-10-19      매수 14종목  /  매도 23종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1439,7 +1439,7 @@
         <v>800</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>5346168809</v>
+        <v>5338077088</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>-230</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-7358253113</v>
+        <v>-7347115992</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>299</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4545697688</v>
+        <v>4538817524</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>-202</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1209709503</v>
+        <v>-1207878541</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>250</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>7006601060</v>
+        <v>6995996184</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>-112</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1181550899</v>
+        <v>-1179762556</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>230</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>10763725628</v>
+        <v>10747434138</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>-108</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-2634217599</v>
+        <v>-2630230565</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>200</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>12373921872</v>
+        <v>12355193261</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>-97</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1859393281</v>
+        <v>-1856578987</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>151</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1331478941</v>
+        <v>1329463675</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-85</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-6112928925</v>
+        <v>-6103676671</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>150</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>3782573072</v>
+        <v>3776847940</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>-65</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1804530273</v>
+        <v>-1801799017</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>99</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>2277277545</v>
+        <v>2273830760</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>-50</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-796505120</v>
+        <v>-795299566</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>85</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>1261353441</v>
+        <v>1259444313</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1805,23 +1805,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2657220402</v>
+        <v>-1989898915</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>4.01%→3.16%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         <v>60</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>4739370717</v>
+        <v>4732197419</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1992915302</v>
+        <v>-2653198553</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.01%→3.16%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>50</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>3592535544</v>
+        <v>3587098043</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>-44</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2245285140</v>
+        <v>-2241886777</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1106249767</v>
+        <v>1104575398</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>-41</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-6897205543</v>
+        <v>-6886766244</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1670677753</v>
+        <v>1668149090</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>-39</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2487673876</v>
+        <v>-2483908645</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>6</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>464815270</v>
+        <v>464111747</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>-30</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-3702261560</v>
+        <v>-3696657984</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>-25</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-716358858</v>
+        <v>-715274610</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>-24</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-3680448557</v>
+        <v>-3674877996</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>-19</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-3271619995</v>
+        <v>-3266668218</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2137,23 +2137,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-4336160656</v>
+        <v>-1092959404</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>5.78%→3.72%</t>
+          <t>2.86%→2.29%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1094616166</v>
+        <v>-4329597638</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.29%</t>
+          <t>5.78%→3.72%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
         <v>-15</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1525918731</v>
+        <v>-1523609169</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2221,23 +2221,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-651481699</v>
+        <v>-1927198949</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.10%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1930120292</v>
+        <v>-650495645</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.10%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
         <v>-7</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1286306195</v>
+        <v>-1284359299</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,142억   ·   현금 1억(0.1%)      주말 2026-10-23  vs  주초 2026-10-19      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,131억      주말 2026-10-23  vs  주초 2026-10-19      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2396,7 +2396,7 @@
         <v>209</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>2066884600</v>
+        <v>2119343810</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>-389</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-3172606200</v>
+        <v>-3253129522</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>104</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>4327065600</v>
+        <v>4436890039</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>-311</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-4938120200</v>
+        <v>-5063453701</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2043678000</v>
+        <v>2095548207</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>-62</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1003990800</v>
+        <v>-1029472902</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>9</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>4826106000</v>
+        <v>4948596490</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>535879400</v>
+        <v>549480454</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 258억   ·   현금 2억(0.9%)      주말 2026-10-23  vs  주초 2026-10-19      매수 9종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 248억      주말 2026-10-23  vs  주초 2026-10-19      매수 9종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B62" s="4" t="n"/>
@@ -2673,11 +2673,11 @@
         <v>199</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>115133440</v>
+        <v>103798368</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>6.94%→7.36%</t>
+          <t>6.52%→6.92%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2694,11 +2694,11 @@
         <v>-26</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-83699200</v>
+        <v>-82284774</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>3.26%→2.92%</t>
+          <t>3.34%→2.99%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2717,11 +2717,11 @@
         <v>61</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>99942400</v>
+        <v>93695971</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.39%</t>
+          <t>0.00%→0.38%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2738,11 +2738,11 @@
         <v>-24</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-87398400</v>
+        <v>-85862373</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>4.56%→4.20%</t>
+          <t>4.67%→4.30%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2761,11 +2761,11 @@
         <v>34</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>30333440</v>
+        <v>30311671</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>0.31%→0.43%</t>
+          <t>0.32%→0.45%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2782,11 +2782,11 @@
         <v>-22</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-45478400</v>
+        <v>-42943987</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.10%</t>
+          <t>0.27%→0.10%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2805,11 +2805,11 @@
         <v>24</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>49612800</v>
+        <v>47923185</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.28%→1.47%</t>
+          <t>1.29%→1.48%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2826,11 +2826,11 @@
         <v>-19</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-27968000</v>
+        <v>-27967991</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>4.92%→4.79%</t>
+          <t>5.12%→4.99%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2849,11 +2849,11 @@
         <v>11</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>23936000</v>
+        <v>23900793</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>7.22%→7.28%</t>
+          <t>7.51%→7.58%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2870,11 +2870,11 @@
         <v>-15</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-61632000</v>
+        <v>-67967979</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.20%</t>
+          <t>1.67%→1.38%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2893,11 +2893,11 @@
         <v>10</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>42944000</v>
+        <v>39871988</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.22%</t>
+          <t>1.03%→1.19%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2914,11 +2914,11 @@
         <v>-6</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-48115200</v>
+        <v>-45004786</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.66%</t>
+          <t>2.79%→2.60%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2930,23 +2930,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>53804800</v>
+        <v>36377589</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.52%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -2958,7 +2958,7 @@
         <v>-3</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-8313600</v>
+        <v>-7891198</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2974,23 +2974,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>37408000</v>
+        <v>48742385</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.22%→1.36%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
@@ -3009,7 +3009,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>22963200</v>
+        <v>22348793</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 863억   ·   현금 2억(0.3%)      주말 2026-10-23  vs  주초 2026-10-19      매수 12종목  /  매도 17종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      주말 2026-10-23  vs  주초 2026-10-19      매수 12종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B79" s="4" t="n"/>
@@ -3160,7 +3160,7 @@
         <v>771</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>1717402500</v>
+        <v>1738218875</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>-430</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-1014585000</v>
+        <v>-1026882631</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>256</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>1113024000</v>
+        <v>1126514795</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>-237</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-521269650</v>
+        <v>-527587880</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>166</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>761442000</v>
+        <v>770671323</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>-223</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-965868750</v>
+        <v>-977575899</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>139</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>347465250</v>
+        <v>351676824</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>-147</v>
       </c>
       <c r="I85" s="15" t="n">
-        <v>-636693750</v>
+        <v>-644411018</v>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>95</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>630135000</v>
+        <v>637772771</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>-108</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-282447000</v>
+        <v>-285870497</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>88</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>685344000</v>
+        <v>693650951</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>-85</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-312056250</v>
+        <v>-315838637</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>341508750</v>
+        <v>345648126</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>-65</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-409158750</v>
+        <v>-414118101</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
@@ -3461,23 +3461,23 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>793914000</v>
+        <v>234300916</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.84%→2.35%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -3489,7 +3489,7 @@
         <v>-57</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-263340000</v>
+        <v>-266531904</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
@@ -3505,23 +3505,23 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>231495000</v>
+        <v>803536911</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>1.84%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -3533,7 +3533,7 @@
         <v>-49</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-523908000</v>
+        <v>-530258209</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>32</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>217536000</v>
+        <v>220172721</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>-41</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-416047500</v>
+        <v>-421090349</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>30</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>242797500</v>
+        <v>245740412</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>-36</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-435996000</v>
+        <v>-441280641</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>6</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>299970000</v>
+        <v>303605891</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>-32</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-630960000</v>
+        <v>-638607771</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>-7</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-285862500</v>
+        <v>-289327396</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>-6</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-214830000</v>
+        <v>-217433922</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>-5</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-139012500</v>
+        <v>-140697449</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
@@ -3770,23 +3770,23 @@
       <c r="E97" s="17" t="n"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-270600000</v>
+        <v>-170005939</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.97%</t>
+          <t>2.57%→2.11%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -3798,23 +3798,23 @@
       <c r="E98" s="17" t="n"/>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-167970000</v>
+        <v>-273879902</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.11%</t>
+          <t>4.46%→3.97%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>586245635</v>
+        <v>2958120178</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.52%</t>
+          <t>1.45%→2.10%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.10%</t>
+          <t>0.43%→0.52%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-795299566</v>
+        <v>-2653198553</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.01%→3.16%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -1805,18 +1805,18 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1989898915</v>
+        <v>-795299566</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-1989898915</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>4.01%→3.16%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2137,23 +2137,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.29%</t>
+          <t>5.78%→3.72%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.78%→3.72%</t>
+          <t>2.86%→2.29%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2221,23 +2221,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-650495645</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.10%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-650495645</v>
+        <v>-1927198949</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.10%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2930,23 +2930,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -2974,23 +2974,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
@@ -3770,23 +3770,23 @@
       <c r="E97" s="17" t="n"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-170005939</v>
+        <v>-273879902</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.11%</t>
+          <t>4.46%→3.97%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -3798,23 +3798,23 @@
       <c r="E98" s="17" t="n"/>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-273879902</v>
+        <v>-170005939</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.97%</t>
+          <t>2.57%→2.11%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2958120178</v>
+        <v>413539225</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.10%</t>
+          <t>1.43%→1.46%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.46%</t>
+          <t>1.45%→2.10%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1761,23 +1761,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-795299566</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>4.01%→3.16%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1805,18 +1805,18 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-795299566</v>
+        <v>-1989898915</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1989898915</v>
+        <v>-2653198553</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.01%→3.16%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2137,23 +2137,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>5.78%→3.72%</t>
+          <t>2.86%→2.29%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.29%</t>
+          <t>5.78%→3.72%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2221,23 +2221,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-650495645</v>
+        <v>-1927198949</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.10%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-650495645</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.10%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2930,23 +2930,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -2974,23 +2974,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>

--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -1761,23 +1761,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-795299566</v>
+        <v>-2653198553</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.01%→3.16%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -1805,18 +1805,18 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1989898915</v>
+        <v>-795299566</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-1989898915</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>4.01%→3.16%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2221,23 +2221,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-650495645</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.10%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-650495645</v>
+        <v>-1927198949</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.10%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2930,23 +2930,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -2974,23 +2974,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
@@ -3461,23 +3461,23 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>234300916</v>
+        <v>803536911</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>1.84%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -3505,23 +3505,23 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>803536911</v>
+        <v>234300916</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.84%→2.35%</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">

--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-10-19 ~ 2026-10-23  (5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>주간 변화  ·  2026-10-19 ~ 2026-10-23  (5거래일)  ·  캡처 9/10  ·  대기: RISE</t>
         </is>
       </c>
     </row>
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.46%</t>
+          <t>1.45%→2.10%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.10%</t>
+          <t>0.43%→0.52%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>586245635</v>
+        <v>413539225</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.52%</t>
+          <t>1.43%→1.46%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1805,18 +1805,18 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-795299566</v>
+        <v>-1989898915</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1849,18 +1849,18 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1989898915</v>
+        <v>-795299566</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -2137,23 +2137,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.29%</t>
+          <t>5.78%→3.72%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.78%→3.72%</t>
+          <t>2.86%→2.29%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2930,23 +2930,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -2974,23 +2974,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
@@ -3045,838 +3045,2172 @@
       <c r="K75" s="20" t="n"/>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B77" s="20" t="n"/>
-      <c r="C77" s="20" t="n"/>
-      <c r="D77" s="20" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="20" t="n"/>
-      <c r="G77" s="20" t="n"/>
-      <c r="H77" s="20" t="n"/>
-      <c r="I77" s="20" t="n"/>
-      <c r="J77" s="20" t="n"/>
-      <c r="K77" s="20" t="n"/>
-    </row>
-    <row r="79" ht="19" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      주말 2026-10-23  vs  주초 2026-10-19      매수 12종목  /  매도 17종목</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="n"/>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="8" t="n"/>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>98996011</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>3.20%→2.42%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>72→75</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>-73311907</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.20%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>277413254</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>6.85%→5.24%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>55→58</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>-105604057</v>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.21%</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>9→6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
-        <v>771</v>
+        <v>3</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>1738218875</v>
+        <v>266503744</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>1.34%→3.65%</t>
+          <t>2.63%→2.17%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>596→1,367</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-430</v>
+        <v>-3</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-1026882631</v>
+        <v>-432639996</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>3.66%→2.00%</t>
+          <t>7.77%→5.22%</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
         <is>
-          <t>1,137→707</t>
+          <t>40→37</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>에프에스티  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B83" s="11" t="n">
-        <v>256</v>
+        <v>3</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>1126514795</v>
+        <v>153979941</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.33%</t>
+          <t>7.12%→5.32%</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>0→256</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>저스템</t>
-        </is>
-      </c>
-      <c r="H83" s="15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="I83" s="15" t="n">
-        <v>-527587880</v>
-      </c>
-      <c r="J83" s="16" t="inlineStr">
-        <is>
-          <t>2.79%→1.86%</t>
-        </is>
-      </c>
-      <c r="K83" s="13" t="inlineStr">
-        <is>
-          <t>942→705</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>에스티아이</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="n">
-        <v>166</v>
-      </c>
-      <c r="C84" s="11" t="n">
-        <v>770671323</v>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>2.12%→2.93%</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>366→532</t>
-        </is>
-      </c>
-      <c r="G84" s="14" t="inlineStr">
-        <is>
-          <t>SFA</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="n">
-        <v>-223</v>
-      </c>
-      <c r="I84" s="15" t="n">
-        <v>-977575899</v>
-      </c>
-      <c r="J84" s="16" t="inlineStr">
-        <is>
-          <t>1.67%→0.50%</t>
-        </is>
-      </c>
-      <c r="K84" s="13" t="inlineStr">
-        <is>
-          <t>320→97</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="C85" s="11" t="n">
-        <v>351676824</v>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>4.89%→5.06%</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>1,550→1,689</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>태웅</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>-147</v>
-      </c>
-      <c r="I85" s="15" t="n">
-        <v>-644411018</v>
-      </c>
-      <c r="J85" s="16" t="inlineStr">
-        <is>
-          <t>1.01%→0.20%</t>
-        </is>
-      </c>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>186→39</t>
-        </is>
-      </c>
+          <t>103→106</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="n"/>
+      <c r="H83" s="17" t="n"/>
+      <c r="I83" s="17" t="n"/>
+      <c r="J83" s="17" t="n"/>
+      <c r="K83" s="17" t="n"/>
+    </row>
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      주말 2026-10-23  vs  주초 2026-10-19      매수 12종목  /  매도 17종목</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="C86" s="11" t="n">
-        <v>637772771</v>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>2.15%→2.94%</t>
-        </is>
-      </c>
-      <c r="E86" s="13" t="inlineStr">
-        <is>
-          <t>275→370</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t>네오셈</t>
-        </is>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>-285870497</v>
-      </c>
-      <c r="J86" s="16" t="inlineStr">
-        <is>
-          <t>2.24%→2.16%</t>
-        </is>
-      </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>797→689</t>
-        </is>
-      </c>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC  (신규)</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="C87" s="11" t="n">
-        <v>693650951</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.82%</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>0→88</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>싸이맥스  (편출)</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="n">
-        <v>-85</v>
-      </c>
-      <c r="I87" s="15" t="n">
-        <v>-315838637</v>
-      </c>
-      <c r="J87" s="16" t="inlineStr">
-        <is>
-          <t>0.36%→0.00%</t>
-        </is>
-      </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>85→0</t>
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>85</v>
+        <v>771</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>345648126</v>
+        <v>1738218875</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>1.46%→1.92%</t>
+          <t>1.34%→3.65%</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>314→399</t>
+          <t>596→1,367</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-65</v>
+        <v>-430</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-414118101</v>
+        <v>-1026882631</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>3.56%→4.27%</t>
+          <t>3.66%→2.00%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>631→566</t>
+          <t>1,137→707</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에프에스티  (신규)</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>803536911</v>
+        <v>1126514795</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>0.00%→1.33%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>0→256</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>원익QnC  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-57</v>
+        <v>-237</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-266531904</v>
+        <v>-527587880</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>2.79%→1.86%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>57→0</t>
+          <t>942→705</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>234300916</v>
+        <v>770671323</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>1.84%→2.35%</t>
+          <t>2.12%→2.93%</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>366→532</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-49</v>
+        <v>-223</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-530258209</v>
+        <v>-977575899</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.49%</t>
+          <t>1.67%→0.50%</t>
         </is>
       </c>
       <c r="K90" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>320→97</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>220172721</v>
+        <v>351676824</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.32%</t>
+          <t>4.89%→5.06%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>376→408</t>
+          <t>1,550→1,689</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>태웅</t>
         </is>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-41</v>
+        <v>-147</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-421090349</v>
+        <v>-644411018</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.40%</t>
+          <t>1.01%→0.20%</t>
         </is>
       </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
-          <t>74→33</t>
+          <t>186→39</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>245740412</v>
+        <v>637772771</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>1.78%→1.90%</t>
+          <t>2.15%→2.94%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>166→196</t>
+          <t>275→370</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>씨엠티엑스  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-36</v>
+        <v>-108</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-441280641</v>
+        <v>-285870497</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>0.50%→0.00%</t>
+          <t>2.24%→2.16%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>36→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
+          <t>RFHIC  (신규)</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>693650951</v>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.82%</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>0→88</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>싸이맥스  (편출)</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>-85</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>-315838637</v>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.00%</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>85→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>345648126</v>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>1.46%→1.92%</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>314→399</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>-414118101</v>
+      </c>
+      <c r="J94" s="16" t="inlineStr">
+        <is>
+          <t>3.56%→4.27%</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="inlineStr">
+        <is>
+          <t>631→566</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>803536911</v>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>1.11%→1.99%</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>50→96</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>원익QnC  (편출)</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>-57</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <v>-266531904</v>
+      </c>
+      <c r="J95" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>57→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>234300916</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>1.84%→2.35%</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>343→389</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <v>-530258209</v>
+      </c>
+      <c r="J96" s="16" t="inlineStr">
+        <is>
+          <t>1.12%→0.49%</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>87→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>220172721</v>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.32%</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>376→408</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <v>-421090349</v>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.40%</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>74→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>245740412</v>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>1.78%→1.90%</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>166→196</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>씨엠티엑스  (편출)</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <v>-441280641</v>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>0.50%→0.00%</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>36→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
           <t>솔브레인</t>
         </is>
       </c>
-      <c r="B93" s="11" t="n">
+      <c r="B99" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C93" s="11" t="n">
+      <c r="C99" s="11" t="n">
         <v>303605891</v>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>2.84%→3.06%</t>
         </is>
       </c>
-      <c r="E93" s="13" t="inlineStr">
+      <c r="E99" s="13" t="inlineStr">
         <is>
           <t>45→51</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
+      <c r="G99" s="14" t="inlineStr">
         <is>
           <t>심텍</t>
         </is>
       </c>
-      <c r="H93" s="15" t="n">
+      <c r="H99" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I93" s="15" t="n">
+      <c r="I99" s="15" t="n">
         <v>-638607771</v>
       </c>
-      <c r="J93" s="16" t="inlineStr">
+      <c r="J99" s="16" t="inlineStr">
         <is>
           <t>6.16%→5.37%</t>
         </is>
       </c>
-      <c r="K93" s="13" t="inlineStr">
+      <c r="K99" s="13" t="inlineStr">
         <is>
           <t>259→227</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="n"/>
-      <c r="B94" s="17" t="n"/>
-      <c r="C94" s="17" t="n"/>
-      <c r="D94" s="17" t="n"/>
-      <c r="E94" s="17" t="n"/>
-      <c r="G94" s="14" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="17" t="n"/>
+      <c r="B100" s="17" t="n"/>
+      <c r="C100" s="17" t="n"/>
+      <c r="D100" s="17" t="n"/>
+      <c r="E100" s="17" t="n"/>
+      <c r="G100" s="14" t="inlineStr">
         <is>
           <t>파크시스템스</t>
         </is>
       </c>
-      <c r="H94" s="15" t="n">
+      <c r="H100" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I94" s="15" t="n">
+      <c r="I100" s="15" t="n">
         <v>-289327396</v>
       </c>
-      <c r="J94" s="16" t="inlineStr">
+      <c r="J100" s="16" t="inlineStr">
         <is>
           <t>1.96%→1.62%</t>
         </is>
       </c>
-      <c r="K94" s="13" t="inlineStr">
+      <c r="K100" s="13" t="inlineStr">
         <is>
           <t>40→33</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="17" t="n"/>
-      <c r="B95" s="17" t="n"/>
-      <c r="C95" s="17" t="n"/>
-      <c r="D95" s="17" t="n"/>
-      <c r="E95" s="17" t="n"/>
-      <c r="G95" s="14" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="17" t="n"/>
+      <c r="B101" s="17" t="n"/>
+      <c r="C101" s="17" t="n"/>
+      <c r="D101" s="17" t="n"/>
+      <c r="E101" s="17" t="n"/>
+      <c r="G101" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H95" s="15" t="n">
+      <c r="H101" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I95" s="15" t="n">
+      <c r="I101" s="15" t="n">
         <v>-217433922</v>
       </c>
-      <c r="J95" s="16" t="inlineStr">
+      <c r="J101" s="16" t="inlineStr">
         <is>
           <t>0.59%→0.30%</t>
         </is>
       </c>
-      <c r="K95" s="13" t="inlineStr">
+      <c r="K101" s="13" t="inlineStr">
         <is>
           <t>13→7</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="17" t="n"/>
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="17" t="n"/>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="17" t="n"/>
-      <c r="G96" s="14" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="17" t="n"/>
+      <c r="B102" s="17" t="n"/>
+      <c r="C102" s="17" t="n"/>
+      <c r="D102" s="17" t="n"/>
+      <c r="E102" s="17" t="n"/>
+      <c r="G102" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H96" s="15" t="n">
+      <c r="H102" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I96" s="15" t="n">
+      <c r="I102" s="15" t="n">
         <v>-140697449</v>
       </c>
-      <c r="J96" s="16" t="inlineStr">
+      <c r="J102" s="16" t="inlineStr">
         <is>
           <t>2.58%→2.13%</t>
         </is>
       </c>
-      <c r="K96" s="13" t="inlineStr">
+      <c r="K102" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="17" t="n"/>
-      <c r="B97" s="17" t="n"/>
-      <c r="C97" s="17" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="17" t="n"/>
-      <c r="G97" s="14" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="17" t="n"/>
+      <c r="B103" s="17" t="n"/>
+      <c r="C103" s="17" t="n"/>
+      <c r="D103" s="17" t="n"/>
+      <c r="E103" s="17" t="n"/>
+      <c r="G103" s="14" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H97" s="15" t="n">
+      <c r="H103" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I97" s="15" t="n">
+      <c r="I103" s="15" t="n">
         <v>-273879902</v>
       </c>
-      <c r="J97" s="16" t="inlineStr">
+      <c r="J103" s="16" t="inlineStr">
         <is>
           <t>4.46%→3.97%</t>
         </is>
       </c>
-      <c r="K97" s="13" t="inlineStr">
+      <c r="K103" s="13" t="inlineStr">
         <is>
           <t>53→49</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="17" t="n"/>
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="17" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="17" t="n"/>
-      <c r="G98" s="14" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="17" t="n"/>
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="17" t="n"/>
+      <c r="D104" s="17" t="n"/>
+      <c r="E104" s="17" t="n"/>
+      <c r="G104" s="14" t="inlineStr">
         <is>
           <t>티에스이</t>
         </is>
       </c>
-      <c r="H98" s="15" t="n">
+      <c r="H104" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I98" s="15" t="n">
+      <c r="I104" s="15" t="n">
         <v>-170005939</v>
       </c>
-      <c r="J98" s="16" t="inlineStr">
+      <c r="J104" s="16" t="inlineStr">
         <is>
           <t>2.57%→2.11%</t>
         </is>
       </c>
-      <c r="K98" s="13" t="inlineStr">
+      <c r="K104" s="13" t="inlineStr">
         <is>
           <t>46→42</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B100" s="20" t="n"/>
-      <c r="C100" s="20" t="n"/>
-      <c r="D100" s="20" t="n"/>
-      <c r="E100" s="20" t="n"/>
-      <c r="F100" s="20" t="n"/>
-      <c r="G100" s="20" t="n"/>
-      <c r="H100" s="20" t="n"/>
-      <c r="I100" s="20" t="n"/>
-      <c r="J100" s="20" t="n"/>
-      <c r="K100" s="20" t="n"/>
-    </row>
-    <row r="102" ht="19" customHeight="1">
-      <c r="A102" s="19" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B102" s="20" t="n"/>
-      <c r="C102" s="20" t="n"/>
-      <c r="D102" s="20" t="n"/>
-      <c r="E102" s="20" t="n"/>
-      <c r="F102" s="20" t="n"/>
-      <c r="G102" s="20" t="n"/>
-      <c r="H102" s="20" t="n"/>
-      <c r="I102" s="20" t="n"/>
-      <c r="J102" s="20" t="n"/>
-      <c r="K102" s="20" t="n"/>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      주말 2026-10-23  vs  주초 2026-10-19      매수 11종목  /  매도 22종목</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>333963630</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.13%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>0→77</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-137</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>-235973595</v>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>1.76%→0.98%</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>305→168</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>1080179100</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>3.56%→7.23%</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>65→131</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-63</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>-232972740</v>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>2.97%→2.21%</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>240→177</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>353496000</v>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>0.53%→1.73%</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>9→29</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>피엠티  (편출)</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>-76168950</v>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.00%</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>53→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>366795000</v>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.24%</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>0→20</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>-237666000</v>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>1.43%→0.64%</t>
+        </is>
+      </c>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>90→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>276726450</v>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>3.41%→4.37%</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>70→89</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>HT로보틱스  (편출)</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>-207773280</v>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>0.70%→0.00%</t>
+        </is>
+      </c>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>48→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>태성</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>288888600</v>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>0.97%→1.95%</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>13→26</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>글로벌텍스프리</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>-110896500</v>
+      </c>
+      <c r="J114" s="16" t="inlineStr">
+        <is>
+          <t>1.05%→0.68%</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>133→86</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>313513200</v>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.06%</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>-132071940</v>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
+        <is>
+          <t>3.28%→2.85%</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>311→269</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>95366700</v>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>0.75%→1.07%</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>21→30</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈  (편출)</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I116" s="15" t="n">
+        <v>-250990740</v>
+      </c>
+      <c r="J116" s="16" t="inlineStr">
+        <is>
+          <t>0.84%→0.00%</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>42→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>127327200</v>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>0.55%→0.98%</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>9→16</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>성호전자  (편출)</t>
+        </is>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>-306949500</v>
+      </c>
+      <c r="J117" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.00%</t>
+        </is>
+      </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>317116800</v>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>2.73%→3.82%</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>18→25</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>큐리언트  (편출)</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>-207979200</v>
+      </c>
+      <c r="J118" s="16" t="inlineStr">
+        <is>
+          <t>0.70%→0.00%</t>
+        </is>
+      </c>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>24→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>153796500</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>5.32%→5.87%</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>31→34</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>엔알비  (편출)</t>
+        </is>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>-85546890</v>
+      </c>
+      <c r="J119" s="16" t="inlineStr">
+        <is>
+          <t>0.29%→0.00%</t>
+        </is>
+      </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>23→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="n"/>
+      <c r="B120" s="17" t="n"/>
+      <c r="C120" s="17" t="n"/>
+      <c r="D120" s="17" t="n"/>
+      <c r="E120" s="17" t="n"/>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>네오티스</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>-175855680</v>
+      </c>
+      <c r="J120" s="16" t="inlineStr">
+        <is>
+          <t>1.23%→0.65%</t>
+        </is>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>44→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="n"/>
+      <c r="B121" s="17" t="n"/>
+      <c r="C121" s="17" t="n"/>
+      <c r="D121" s="17" t="n"/>
+      <c r="E121" s="17" t="n"/>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>-81750240</v>
+      </c>
+      <c r="J121" s="16" t="inlineStr">
+        <is>
+          <t>0.91%→0.64%</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>40→28</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="n"/>
+      <c r="B122" s="17" t="n"/>
+      <c r="C122" s="17" t="n"/>
+      <c r="D122" s="17" t="n"/>
+      <c r="E122" s="17" t="n"/>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>-123552000</v>
+      </c>
+      <c r="J122" s="16" t="inlineStr">
+        <is>
+          <t>1.21%→0.80%</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>35→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="n"/>
+      <c r="B123" s="17" t="n"/>
+      <c r="C123" s="17" t="n"/>
+      <c r="D123" s="17" t="n"/>
+      <c r="E123" s="17" t="n"/>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-110660550</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>0.91%→0.54%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>27→16</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="n"/>
+      <c r="B124" s="17" t="n"/>
+      <c r="C124" s="17" t="n"/>
+      <c r="D124" s="17" t="n"/>
+      <c r="E124" s="17" t="n"/>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-553066800</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>2.86%→1.02%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>17→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="n"/>
+      <c r="B125" s="17" t="n"/>
+      <c r="C125" s="17" t="n"/>
+      <c r="D125" s="17" t="n"/>
+      <c r="E125" s="17" t="n"/>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>덕산테코피아</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-43886700</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.19%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>23→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="n"/>
+      <c r="B126" s="17" t="n"/>
+      <c r="C126" s="17" t="n"/>
+      <c r="D126" s="17" t="n"/>
+      <c r="E126" s="17" t="n"/>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-77177100</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.78%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="n"/>
+      <c r="B127" s="17" t="n"/>
+      <c r="C127" s="17" t="n"/>
+      <c r="D127" s="17" t="n"/>
+      <c r="E127" s="17" t="n"/>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-117331500</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.40%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>10→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="n"/>
+      <c r="B128" s="17" t="n"/>
+      <c r="C128" s="17" t="n"/>
+      <c r="D128" s="17" t="n"/>
+      <c r="E128" s="17" t="n"/>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>-119776800</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
+        <is>
+          <t>3.61%→3.23%</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>36→32</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="n"/>
+      <c r="B129" s="17" t="n"/>
+      <c r="C129" s="17" t="n"/>
+      <c r="D129" s="17" t="n"/>
+      <c r="E129" s="17" t="n"/>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>-179493600</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t>1.05%→0.45%</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>7→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="n"/>
+      <c r="B130" s="17" t="n"/>
+      <c r="C130" s="17" t="n"/>
+      <c r="D130" s="17" t="n"/>
+      <c r="E130" s="17" t="n"/>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>-18815940</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.30%</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>17→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
+      <c r="K132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="6" t="n"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="8" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>28441600</v>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.51%</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>-27283200</v>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>3.44%→2.93%</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>21974400</v>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>3.18%→3.57%</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I136" s="15" t="n">
+        <v>-24371200</v>
+      </c>
+      <c r="J136" s="16" t="inlineStr">
+        <is>
+          <t>4.36%→3.90%</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>9792000</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>2.61%→2.78%</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I137" s="15" t="n">
+        <v>-25612000</v>
+      </c>
+      <c r="J137" s="16" t="inlineStr">
+        <is>
+          <t>4.92%→4.44%</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>36080000</v>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>5.99%→6.62%</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="n"/>
+      <c r="H138" s="17" t="n"/>
+      <c r="I138" s="17" t="n"/>
+      <c r="J138" s="17" t="n"/>
+      <c r="K138" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="29">
     <mergeCell ref="A77:K77"/>
+    <mergeCell ref="G86:K86"/>
     <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="G27:K27"/>
+    <mergeCell ref="G107:K107"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A79:K79"/>
+    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="G78:K78"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="G133:K133"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G80:K80"/>
+    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A106:K106"/>
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A100:K100"/>
     <mergeCell ref="G63:K63"/>
     <mergeCell ref="G54:K54"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A102:K102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20261023.xlsx
+++ b/reports/pdf_weekly_20261023.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.10%</t>
+          <t>0.43%→0.52%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>586245635</v>
+        <v>413539225</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.52%</t>
+          <t>1.43%→1.46%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.46%</t>
+          <t>1.45%→2.10%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-795299566</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>4.01%→3.16%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-795299566</v>
+        <v>-2653198553</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.01%→3.16%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B77" s="4" t="n"/>
@@ -3136,23 +3136,23 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>98996011</v>
+        <v>266503744</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>3.20%→2.42%</t>
+          <t>2.63%→2.17%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -3180,23 +3180,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>277413254</v>
+        <v>153979941</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>6.85%→5.24%</t>
+          <t>7.12%→5.32%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3224,23 +3224,23 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>266503744</v>
+        <v>98996011</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2.63%→2.17%</t>
+          <t>3.20%→2.42%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -3268,23 +3268,23 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B83" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>153979941</v>
+        <v>277413254</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>7.12%→5.32%</t>
+          <t>6.85%→5.24%</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G83" s="17" t="n"/>
@@ -3693,23 +3693,23 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B95" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>803536911</v>
+        <v>234300916</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.84%→2.35%</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -3737,23 +3737,23 @@
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>234300916</v>
+        <v>803536911</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>1.84%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -4053,7 +4053,7 @@
     <row r="106" ht="19" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      주말 2026-10-23  vs  주초 2026-10-19      매수 11종목  /  매도 22종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억      주말 2026-10-23  vs  주초 2026-10-19      매수 11종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B106" s="4" t="n"/>
@@ -4406,88 +4406,88 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B115" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>313513200</v>
+        <v>95366700</v>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.75%→1.07%</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>LS머트리얼즈  (편출)</t>
         </is>
       </c>
       <c r="H115" s="15" t="n">
         <v>-42</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>-132071940</v>
+        <v>-250990740</v>
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>3.28%→2.85%</t>
+          <t>0.84%→0.00%</t>
         </is>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
-          <t>311→269</t>
+          <t>42→0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>95366700</v>
+        <v>313513200</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>0.75%→1.07%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>LS머트리얼즈  (편출)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-42</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-250990740</v>
+        <v>-132071940</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>0.84%→0.00%</t>
+          <t>3.28%→2.85%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>42→0</t>
+          <t>311→269</t>
         </is>
       </c>
     </row>
@@ -4659,23 +4659,23 @@
       <c r="E121" s="17" t="n"/>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-81750240</v>
+        <v>-123552000</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.64%</t>
+          <t>1.21%→0.80%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>40→28</t>
+          <t>35→23</t>
         </is>
       </c>
     </row>
@@ -4687,23 +4687,23 @@
       <c r="E122" s="17" t="n"/>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-123552000</v>
+        <v>-81750240</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>1.21%→0.80%</t>
+          <t>0.91%→0.64%</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>35→23</t>
+          <t>40→28</t>
         </is>
       </c>
     </row>
@@ -4855,23 +4855,23 @@
       <c r="E128" s="17" t="n"/>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H128" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I128" s="15" t="n">
-        <v>-119776800</v>
+        <v>-179493600</v>
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>3.61%→3.23%</t>
+          <t>1.05%→0.45%</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>
@@ -4883,23 +4883,23 @@
       <c r="E129" s="17" t="n"/>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H129" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>-179493600</v>
+        <v>-119776800</v>
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.45%</t>
+          <t>3.61%→3.23%</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="132" ht="19" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억      주말 2026-10-23  vs  주초 2026-10-19      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B132" s="4" t="n"/>
